--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2374,6 +2374,210 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123762874</v>
+      </c>
+      <c r="B17" t="n">
+        <v>95689</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jonas, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>570810</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6702288</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123762873</v>
+      </c>
+      <c r="B18" t="n">
+        <v>95689</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jonas, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>570790</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6702254</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -2379,7 +2379,7 @@
         <v>123762874</v>
       </c>
       <c r="B17" t="n">
-        <v>95689</v>
+        <v>95695</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>123762873</v>
       </c>
       <c r="B18" t="n">
-        <v>95689</v>
+        <v>95695</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -2379,7 +2379,7 @@
         <v>123762874</v>
       </c>
       <c r="B17" t="n">
-        <v>95695</v>
+        <v>95697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>123762873</v>
       </c>
       <c r="B18" t="n">
-        <v>95695</v>
+        <v>95697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -2379,7 +2379,7 @@
         <v>123762874</v>
       </c>
       <c r="B17" t="n">
-        <v>95697</v>
+        <v>96205</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>123762873</v>
       </c>
       <c r="B18" t="n">
-        <v>95697</v>
+        <v>96205</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -2376,7 +2376,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123762874</v>
+        <v>123762873</v>
       </c>
       <c r="B17" t="n">
         <v>96205</v>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570810</v>
+        <v>570790</v>
       </c>
       <c r="R17" t="n">
-        <v>6702288</v>
+        <v>6702254</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123762873</v>
+        <v>123762874</v>
       </c>
       <c r="B18" t="n">
         <v>96205</v>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570790</v>
+        <v>570810</v>
       </c>
       <c r="R18" t="n">
-        <v>6702254</v>
+        <v>6702288</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -2376,7 +2376,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123762873</v>
+        <v>123762874</v>
       </c>
       <c r="B17" t="n">
         <v>96205</v>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570790</v>
+        <v>570810</v>
       </c>
       <c r="R17" t="n">
-        <v>6702254</v>
+        <v>6702288</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123762874</v>
+        <v>123762873</v>
       </c>
       <c r="B18" t="n">
         <v>96205</v>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570810</v>
+        <v>570790</v>
       </c>
       <c r="R18" t="n">
-        <v>6702288</v>
+        <v>6702254</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -2376,7 +2376,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123762873</v>
+        <v>123762874</v>
       </c>
       <c r="B17" t="n">
         <v>96227</v>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570790</v>
+        <v>570810</v>
       </c>
       <c r="R17" t="n">
-        <v>6702254</v>
+        <v>6702288</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,7 +2478,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123762874</v>
+        <v>123762873</v>
       </c>
       <c r="B18" t="n">
         <v>96227</v>
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570810</v>
+        <v>570790</v>
       </c>
       <c r="R18" t="n">
-        <v>6702288</v>
+        <v>6702254</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2578,6 +2578,208 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128473407</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92295</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Övre Stigsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>570745</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6702185</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128473402</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92295</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Övre Stigsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>570737</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6702187</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -2583,7 +2583,7 @@
         <v>128473407</v>
       </c>
       <c r="B19" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>128473402</v>
       </c>
       <c r="B20" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2780,6 +2780,1038 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128626135</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91225</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Jonas, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>570844</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6702268</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128626134</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91225</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Jonas, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>570829</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6702290</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128626097</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Jonas, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>570767</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6702183</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128626136</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91225</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Jonas, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>570850</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6702251</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128626116</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Jonas, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>570845</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6702268</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128626133</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91225</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Jonas, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>570818</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6702329</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128626095</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Jonas, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>570847</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6702259</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128626122</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Jonas, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>570844</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6702221</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128626110</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Jonas, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>570780</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6702360</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -2583,7 +2583,7 @@
         <v>128473407</v>
       </c>
       <c r="B19" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>128473402</v>
       </c>
       <c r="B20" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>128626135</v>
       </c>
       <c r="B21" t="n">
-        <v>91225</v>
+        <v>91231</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>128626134</v>
       </c>
       <c r="B22" t="n">
-        <v>91225</v>
+        <v>91231</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>128626097</v>
       </c>
       <c r="B23" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>128626136</v>
       </c>
       <c r="B24" t="n">
-        <v>91225</v>
+        <v>91231</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>128626116</v>
       </c>
       <c r="B25" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>128626133</v>
       </c>
       <c r="B26" t="n">
-        <v>91225</v>
+        <v>91231</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128626095</v>
       </c>
       <c r="B27" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128626122</v>
       </c>
       <c r="B28" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>128626110</v>
       </c>
       <c r="B29" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -2583,7 +2583,7 @@
         <v>128473407</v>
       </c>
       <c r="B19" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>128473402</v>
       </c>
       <c r="B20" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>128626135</v>
       </c>
       <c r="B21" t="n">
-        <v>91231</v>
+        <v>91237</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>128626134</v>
       </c>
       <c r="B22" t="n">
-        <v>91231</v>
+        <v>91237</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>128626097</v>
       </c>
       <c r="B23" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>128626136</v>
       </c>
       <c r="B24" t="n">
-        <v>91231</v>
+        <v>91237</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>128626116</v>
       </c>
       <c r="B25" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>128626133</v>
       </c>
       <c r="B26" t="n">
-        <v>91231</v>
+        <v>91237</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128626095</v>
       </c>
       <c r="B27" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128626122</v>
       </c>
       <c r="B28" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>128626110</v>
       </c>
       <c r="B29" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -2583,7 +2583,7 @@
         <v>128473407</v>
       </c>
       <c r="B19" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>128473402</v>
       </c>
       <c r="B20" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>128626135</v>
       </c>
       <c r="B21" t="n">
-        <v>91237</v>
+        <v>91239</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>128626134</v>
       </c>
       <c r="B22" t="n">
-        <v>91237</v>
+        <v>91239</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>128626097</v>
       </c>
       <c r="B23" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>128626136</v>
       </c>
       <c r="B24" t="n">
-        <v>91237</v>
+        <v>91239</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>128626116</v>
       </c>
       <c r="B25" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>128626133</v>
       </c>
       <c r="B26" t="n">
-        <v>91237</v>
+        <v>91239</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128626095</v>
       </c>
       <c r="B27" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128626122</v>
       </c>
       <c r="B28" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>128626110</v>
       </c>
       <c r="B29" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -2583,7 +2583,7 @@
         <v>128473407</v>
       </c>
       <c r="B19" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>128473402</v>
       </c>
       <c r="B20" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>128626135</v>
       </c>
       <c r="B21" t="n">
-        <v>91239</v>
+        <v>91240</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>128626134</v>
       </c>
       <c r="B22" t="n">
-        <v>91239</v>
+        <v>91240</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>128626097</v>
       </c>
       <c r="B23" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>128626136</v>
       </c>
       <c r="B24" t="n">
-        <v>91239</v>
+        <v>91240</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>128626116</v>
       </c>
       <c r="B25" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>128626133</v>
       </c>
       <c r="B26" t="n">
-        <v>91239</v>
+        <v>91240</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128626095</v>
       </c>
       <c r="B27" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128626122</v>
       </c>
       <c r="B28" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>128626110</v>
       </c>
       <c r="B29" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -2583,7 +2583,7 @@
         <v>128473407</v>
       </c>
       <c r="B19" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>128473402</v>
       </c>
       <c r="B20" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>128626135</v>
       </c>
       <c r="B21" t="n">
-        <v>91240</v>
+        <v>91267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>128626134</v>
       </c>
       <c r="B22" t="n">
-        <v>91240</v>
+        <v>91267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>128626097</v>
       </c>
       <c r="B23" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>128626136</v>
       </c>
       <c r="B24" t="n">
-        <v>91240</v>
+        <v>91267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>128626116</v>
       </c>
       <c r="B25" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>128626133</v>
       </c>
       <c r="B26" t="n">
-        <v>91240</v>
+        <v>91267</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128626095</v>
       </c>
       <c r="B27" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128626122</v>
       </c>
       <c r="B28" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>128626110</v>
       </c>
       <c r="B29" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -2583,7 +2583,7 @@
         <v>128473407</v>
       </c>
       <c r="B19" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>128473402</v>
       </c>
       <c r="B20" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>128626135</v>
       </c>
       <c r="B21" t="n">
-        <v>91267</v>
+        <v>91272</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>128626134</v>
       </c>
       <c r="B22" t="n">
-        <v>91267</v>
+        <v>91272</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>128626097</v>
       </c>
       <c r="B23" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>128626136</v>
       </c>
       <c r="B24" t="n">
-        <v>91267</v>
+        <v>91272</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>128626116</v>
       </c>
       <c r="B25" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>128626133</v>
       </c>
       <c r="B26" t="n">
-        <v>91267</v>
+        <v>91272</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128626095</v>
       </c>
       <c r="B27" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128626122</v>
       </c>
       <c r="B28" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>128626110</v>
       </c>
       <c r="B29" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -2785,7 +2785,7 @@
         <v>128626135</v>
       </c>
       <c r="B21" t="n">
-        <v>91288</v>
+        <v>91293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>128626134</v>
       </c>
       <c r="B22" t="n">
-        <v>91288</v>
+        <v>91293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>128626097</v>
       </c>
       <c r="B23" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>128626136</v>
       </c>
       <c r="B24" t="n">
-        <v>91288</v>
+        <v>91293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>128626116</v>
       </c>
       <c r="B25" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>128626133</v>
       </c>
       <c r="B26" t="n">
-        <v>91288</v>
+        <v>91293</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128626095</v>
       </c>
       <c r="B27" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128626122</v>
       </c>
       <c r="B28" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>128626110</v>
       </c>
       <c r="B29" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -2785,7 +2785,7 @@
         <v>128626135</v>
       </c>
       <c r="B21" t="n">
-        <v>91293</v>
+        <v>91299</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>128626134</v>
       </c>
       <c r="B22" t="n">
-        <v>91293</v>
+        <v>91299</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>128626097</v>
       </c>
       <c r="B23" t="n">
-        <v>92456</v>
+        <v>92464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>128626136</v>
       </c>
       <c r="B24" t="n">
-        <v>91293</v>
+        <v>91299</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>128626116</v>
       </c>
       <c r="B25" t="n">
-        <v>92456</v>
+        <v>92464</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>128626133</v>
       </c>
       <c r="B26" t="n">
-        <v>91293</v>
+        <v>91299</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>128626095</v>
       </c>
       <c r="B27" t="n">
-        <v>92456</v>
+        <v>92464</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>128626122</v>
       </c>
       <c r="B28" t="n">
-        <v>92456</v>
+        <v>92464</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>128626110</v>
       </c>
       <c r="B29" t="n">
-        <v>92456</v>
+        <v>92464</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95889662</v>
+        <v>128473428</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Övre Stigsbo, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570812.4102701787</v>
+        <v>570700</v>
       </c>
       <c r="R2" t="n">
-        <v>6702140.802233334</v>
+        <v>6702186</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>18:26</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18:26</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95889096</v>
+        <v>95888326</v>
       </c>
       <c r="B3" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570779.2839103466</v>
+        <v>570864</v>
       </c>
       <c r="R3" t="n">
-        <v>6702267.492608979</v>
+        <v>6702207</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +844,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +854,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,15 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95888703</v>
+        <v>95888543</v>
       </c>
       <c r="B4" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -950,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570854.2314352769</v>
+        <v>570853</v>
       </c>
       <c r="R4" t="n">
-        <v>6702252.176941103</v>
+        <v>6702281</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,7 +953,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +963,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,57 +990,47 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95889027</v>
+        <v>95888703</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570784.242890812</v>
+        <v>570854</v>
       </c>
       <c r="R5" t="n">
-        <v>6702342.608063775</v>
+        <v>6702253</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1104,7 +1062,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1072,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95889769</v>
+        <v>95888746</v>
       </c>
       <c r="B6" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570791.5752623524</v>
+        <v>570824</v>
       </c>
       <c r="R6" t="n">
-        <v>6702220.351817612</v>
+        <v>6702270</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1171,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1181,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,12 +1211,7 @@
         <v>95888830</v>
       </c>
       <c r="B7" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570784.242890812</v>
+        <v>570784</v>
       </c>
       <c r="R7" t="n">
-        <v>6702342.608063775</v>
+        <v>6702342</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1369,15 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95888520</v>
+        <v>95889096</v>
       </c>
       <c r="B8" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,35 +1328,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570866.2652453339</v>
+        <v>570779</v>
       </c>
       <c r="R8" t="n">
-        <v>6702243.528386215</v>
+        <v>6702267</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1445,7 +1389,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1399,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,15 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95889712</v>
+        <v>95889255</v>
       </c>
       <c r="B9" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570819.5576813286</v>
+        <v>570743</v>
       </c>
       <c r="R9" t="n">
-        <v>6702205.104912767</v>
+        <v>6702163</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1559,7 +1498,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1508,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,15 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95888326</v>
+        <v>95889712</v>
       </c>
       <c r="B10" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570864.0046778037</v>
+        <v>570820</v>
       </c>
       <c r="R10" t="n">
-        <v>6702207.454689563</v>
+        <v>6702205</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1673,7 +1607,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1617,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,15 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95888798</v>
+        <v>95889769</v>
       </c>
       <c r="B11" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,35 +1655,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3215</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570816.3030010952</v>
+        <v>570792</v>
       </c>
       <c r="R11" t="n">
-        <v>6702321.025335032</v>
+        <v>6702220</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,7 +1716,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1726,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,15 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95889255</v>
+        <v>116967285</v>
       </c>
       <c r="B12" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,21 +1782,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Stigsbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570742.2676212132</v>
+        <v>570787</v>
       </c>
       <c r="R12" t="n">
-        <v>6702163.123024757</v>
+        <v>6702327</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,22 +1818,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:53</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:53</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,15 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95888746</v>
+        <v>123762873</v>
       </c>
       <c r="B13" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,21 +1879,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedemora, Dlr</t>
+          <t>Jonas, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570824.2243224897</v>
+        <v>570790</v>
       </c>
       <c r="R13" t="n">
-        <v>6702269.851531294</v>
+        <v>6702254</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2009,22 +1915,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>17:22</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-09-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>17:22</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,15 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110158879</v>
+        <v>123762874</v>
       </c>
       <c r="B14" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,38 +1958,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6439</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stigsboån, Dlr</t>
+          <t>Jonas, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570848.4171627985</v>
+        <v>570810</v>
       </c>
       <c r="R14" t="n">
-        <v>6702246.140618565</v>
+        <v>6702288</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2122,22 +2012,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:49</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,61 +2044,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112439580</v>
+        <v>95888474</v>
       </c>
       <c r="B15" t="n">
-        <v>56656</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stigsbo, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>570818</v>
+        <v>570866</v>
       </c>
       <c r="R15" t="n">
-        <v>6702190</v>
+        <v>6702243</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2242,12 +2110,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,15 +2152,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>116967285</v>
+        <v>95888555</v>
       </c>
       <c r="B16" t="n">
-        <v>95074</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2290,37 +2163,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>3215</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stigsbo, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>570787</v>
+        <v>570859</v>
       </c>
       <c r="R16" t="n">
-        <v>6702327</v>
+        <v>6702277</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2344,12 +2218,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,15 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123762874</v>
+        <v>95888798</v>
       </c>
       <c r="B17" t="n">
-        <v>96227</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,37 +2271,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jonas, Dlr</t>
+          <t>Hedemora, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>570810</v>
+        <v>570817</v>
       </c>
       <c r="R17" t="n">
-        <v>6702288</v>
+        <v>6702321</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2446,12 +2326,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,15 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123762873</v>
+        <v>128626133</v>
       </c>
       <c r="B18" t="n">
-        <v>96227</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,21 +2379,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>3215</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2518,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>570790</v>
+        <v>570818</v>
       </c>
       <c r="R18" t="n">
-        <v>6702254</v>
+        <v>6702329</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2548,12 +2433,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,6 +2462,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2580,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128473407</v>
+        <v>128626134</v>
       </c>
       <c r="B19" t="n">
-        <v>92451</v>
+        <v>91680</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,38 +2492,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Övre Stigsbo, Dlr</t>
+          <t>Jonas, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570745</v>
+        <v>570829</v>
       </c>
       <c r="R19" t="n">
-        <v>6702185</v>
+        <v>6702290</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2649,12 +2546,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2663,6 +2575,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2681,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128473402</v>
+        <v>128626135</v>
       </c>
       <c r="B20" t="n">
-        <v>92451</v>
+        <v>91680</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2692,38 +2605,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Övre Stigsbo, Dlr</t>
+          <t>Jonas, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570737</v>
+        <v>570844</v>
       </c>
       <c r="R20" t="n">
-        <v>6702187</v>
+        <v>6702268</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2750,12 +2659,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,6 +2688,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2782,10 +2707,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128626135</v>
+        <v>128626136</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>91680</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570844</v>
+        <v>570850</v>
       </c>
       <c r="R21" t="n">
-        <v>6702268</v>
+        <v>6702251</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2852,7 +2777,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2862,7 +2787,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2895,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128626134</v>
+        <v>128473402</v>
       </c>
       <c r="B22" t="n">
-        <v>91299</v>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,34 +2831,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Jonas, Dlr</t>
+          <t>Övre Stigsbo, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570829</v>
+        <v>570737</v>
       </c>
       <c r="R22" t="n">
-        <v>6702290</v>
+        <v>6702187</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,27 +2889,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2989,7 +2903,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3008,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128626097</v>
+        <v>128473405</v>
       </c>
       <c r="B23" t="n">
-        <v>92464</v>
+        <v>92869</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3038,24 +2951,19 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Jonas, Dlr</t>
+          <t>Övre Stigsbo, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>570767</v>
+        <v>570698</v>
       </c>
       <c r="R23" t="n">
-        <v>6702183</v>
+        <v>6702176</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,22 +2990,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:58</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:58</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3124,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128626136</v>
+        <v>128473406</v>
       </c>
       <c r="B24" t="n">
-        <v>91299</v>
+        <v>92869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,34 +3033,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Jonas, Dlr</t>
+          <t>Övre Stigsbo, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>570850</v>
+        <v>570706</v>
       </c>
       <c r="R24" t="n">
-        <v>6702251</v>
+        <v>6702192</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3189,27 +3091,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3218,7 +3105,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3237,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128626116</v>
+        <v>128473407</v>
       </c>
       <c r="B25" t="n">
-        <v>92464</v>
+        <v>92869</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,24 +3153,19 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Jonas, Dlr</t>
+          <t>Övre Stigsbo, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>570845</v>
+        <v>570745</v>
       </c>
       <c r="R25" t="n">
-        <v>6702268</v>
+        <v>6702185</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3311,22 +3192,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3353,10 +3224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128626133</v>
+        <v>128626095</v>
       </c>
       <c r="B26" t="n">
-        <v>91299</v>
+        <v>92869</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3364,34 +3235,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jonas, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>570818</v>
+        <v>570847</v>
       </c>
       <c r="R26" t="n">
-        <v>6702329</v>
+        <v>6702259</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3423,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3433,12 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3447,7 +3322,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3466,10 +3340,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128626095</v>
+        <v>128626097</v>
       </c>
       <c r="B27" t="n">
-        <v>92464</v>
+        <v>92869</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3510,10 +3384,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>570847</v>
+        <v>570767</v>
       </c>
       <c r="R27" t="n">
-        <v>6702259</v>
+        <v>6702183</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3545,7 +3419,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3555,7 +3429,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3582,10 +3456,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128626122</v>
+        <v>128626107</v>
       </c>
       <c r="B28" t="n">
-        <v>92464</v>
+        <v>92869</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3612,7 +3486,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3626,10 +3500,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>570844</v>
+        <v>570714</v>
       </c>
       <c r="R28" t="n">
-        <v>6702221</v>
+        <v>6702171</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3661,7 +3535,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3671,7 +3545,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3701,7 +3575,7 @@
         <v>128626110</v>
       </c>
       <c r="B29" t="n">
-        <v>92464</v>
+        <v>92869</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3811,6 +3685,1011 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128626116</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Jonas, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>570845</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6702268</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128626118</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Jonas, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>570699</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6702174</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128626122</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Jonas, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>570844</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6702221</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>95888202</v>
+      </c>
+      <c r="B33" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>570893</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6702243</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>95889189</v>
+      </c>
+      <c r="B34" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>570708</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6702189</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>110158879</v>
+      </c>
+      <c r="B35" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stigsboån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>570848</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6702247</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>95889027</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>570784</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6702342</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>95889662</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hedemora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>570813</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6702140</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2021-09-03</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>112439580</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stigsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>570818</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6702190</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45872-2021 artfynd.xlsx
+++ b/artfynd/A 45872-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128473428</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95888326</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95888543</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95888703</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95888746</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95888830</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95889096</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95889255</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95889712</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1750,6 +1800,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95889769</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1847,6 +1902,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116967285</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123762873</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2041,6 +2106,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123762874</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2149,6 +2219,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95888474</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2257,6 +2332,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95888555</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2365,6 +2445,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95888798</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2478,6 +2563,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626133</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2591,6 +2681,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626134</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2704,6 +2799,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626135</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2817,6 +2917,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626136</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2918,6 +3023,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128473402</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3019,6 +3129,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128473405</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3120,6 +3235,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128473406</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3221,6 +3341,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128473407</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3337,6 +3462,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626095</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3453,6 +3583,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626097</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3569,6 +3704,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626107</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3685,6 +3825,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626110</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3801,6 +3946,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626116</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3917,6 +4067,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626118</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4033,6 +4188,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626122</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4141,6 +4301,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95888202</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4249,6 +4414,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95889189</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4357,6 +4527,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110158879</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4471,6 +4646,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95889027</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4585,6 +4765,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95889662</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4690,8 +4875,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112439580</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>